--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4031,7 +4031,7 @@
         <v>0.002571860816944024</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7579,7 +7579,7 @@
         <v>0.006376456161863887</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>19069</v>
@@ -11127,7 +11127,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -14666,16 +14666,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>300838</v>
+        <v>300827</v>
       </c>
       <c r="C56" t="n">
         <v>9415</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.03886889115839877</v>
+        <v>0.03883205812921697</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>182377</v>
@@ -14690,10 +14690,10 @@
         <v>0.6359744732977259</v>
       </c>
       <c r="J56" t="n">
-        <v>25869</v>
+        <v>25883</v>
       </c>
       <c r="K56" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57">
@@ -14709,7 +14709,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.1233767280251923</v>
+        <v>-0.1233456463019191</v>
       </c>
       <c r="E57" t="n">
         <v>4</v>
@@ -18223,7 +18223,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -21290,7 +21290,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>4406</v>
@@ -24616,7 +24616,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>24863</v>
@@ -27683,7 +27683,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -30787,7 +30787,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -34335,7 +34335,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -37883,7 +37883,7 @@
         <v>0.007653246282190787</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -41431,7 +41431,7 @@
         <v>0.08366063523054919</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>36442</v>
@@ -41449,7 +41449,7 @@
         <v>2947</v>
       </c>
       <c r="K56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -44979,7 +44979,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -48527,7 +48527,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -52075,7 +52075,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -55623,7 +55623,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -59184,7 +59184,7 @@
         <v>0.01003118423276034</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>62096</v>
@@ -62732,7 +62732,7 @@
         <v>-0.0005308499666322878</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>51839</v>
@@ -66280,7 +66280,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>14529</v>
@@ -69347,7 +69347,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -71970,7 +71970,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -75074,7 +75074,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -78622,7 +78622,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>104677</v>
@@ -78640,7 +78640,7 @@
         <v>12405</v>
       </c>
       <c r="K56" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4031,7 +4031,7 @@
         <v>0.002571860816944024</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7579,7 +7579,7 @@
         <v>0.006376456161863887</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>19069</v>
@@ -11127,7 +11127,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
         <v>0.03883205812921697</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>182377</v>
@@ -18223,7 +18223,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -21290,7 +21290,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
         <v>4406</v>
@@ -24616,7 +24616,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>24863</v>
@@ -27683,7 +27683,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -30787,7 +30787,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -34335,7 +34335,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -37883,7 +37883,7 @@
         <v>0.007653246282190787</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -41431,7 +41431,7 @@
         <v>0.08366063523054919</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>36442</v>
@@ -44979,7 +44979,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -48527,7 +48527,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -52075,7 +52075,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -55623,7 +55623,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -59184,7 +59184,7 @@
         <v>0.01003118423276034</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>62096</v>
@@ -62732,7 +62732,7 @@
         <v>-0.0005308499666322878</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>51839</v>
@@ -66280,7 +66280,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>14529</v>
@@ -69347,7 +69347,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -71970,7 +71970,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -75074,7 +75074,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -78622,7 +78622,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>104677</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -41446,10 +41446,10 @@
         <v>0.2926124288021763</v>
       </c>
       <c r="J56" t="n">
-        <v>2947</v>
+        <v>2949</v>
       </c>
       <c r="K56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -14693,7 +14693,7 @@
         <v>25883</v>
       </c>
       <c r="K56" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57">
@@ -41440,10 +41440,10 @@
         <v>1929</v>
       </c>
       <c r="H56" t="n">
-        <v>7244</v>
+        <v>9138</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.2926124288021763</v>
+        <v>0.3462835444472782</v>
       </c>
       <c r="J56" t="n">
         <v>2949</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4031,7 +4031,7 @@
         <v>0.002571860816944024</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -4049,7 +4049,7 @@
         <v>1122</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -7579,7 +7579,7 @@
         <v>0.006376456161863887</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>19069</v>
@@ -7594,10 +7594,10 @@
         <v>0.05567409318711854</v>
       </c>
       <c r="J56" t="n">
-        <v>1091</v>
+        <v>1099</v>
       </c>
       <c r="K56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -11127,7 +11127,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
         <v>0.03883205812921697</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>182377</v>
@@ -18223,7 +18223,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -18238,10 +18238,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1395</v>
+        <v>1403</v>
       </c>
       <c r="K56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -21290,7 +21290,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F43" t="n">
         <v>4406</v>
@@ -24616,7 +24616,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>24863</v>
@@ -24631,10 +24631,10 @@
         <v>0.01283491095780523</v>
       </c>
       <c r="J56" t="n">
-        <v>1891</v>
+        <v>1902</v>
       </c>
       <c r="K56" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -27683,7 +27683,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -30787,7 +30787,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -34335,7 +34335,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -37874,16 +37874,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>27781</v>
+        <v>28577</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.007653246282190787</v>
+        <v>0.03652520856002902</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -37898,10 +37898,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1715</v>
+        <v>1723</v>
       </c>
       <c r="K56" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -37917,7 +37917,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.06428854252906663</v>
+        <v>-0.09035238128564931</v>
       </c>
       <c r="E57" t="n">
         <v>4</v>
@@ -41422,16 +41422,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>45533</v>
+        <v>45584</v>
       </c>
       <c r="C56" t="n">
         <v>2199</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.08366063523054919</v>
+        <v>0.08481848934093128</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>36442</v>
@@ -41449,7 +41449,7 @@
         <v>2949</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -41465,7 +41465,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.2690438280398894</v>
+        <v>-0.2698239959818345</v>
       </c>
       <c r="E57" t="n">
         <v>4</v>
@@ -44979,7 +44979,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -48527,7 +48527,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -52075,7 +52075,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -55623,7 +55623,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -59184,7 +59184,7 @@
         <v>0.01003118423276034</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>62096</v>
@@ -59199,10 +59199,10 @@
         <v>0.06484818964117552</v>
       </c>
       <c r="J56" t="n">
-        <v>4183</v>
+        <v>4226</v>
       </c>
       <c r="K56" t="n">
-        <v>56</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">
@@ -62723,16 +62723,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>65897</v>
+        <v>66194</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>-0.0005308499666322878</v>
+        <v>0.003973791178790269</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>51839</v>
@@ -62747,10 +62747,10 @@
         <v>0.004243499729959108</v>
       </c>
       <c r="J56" t="n">
-        <v>4531</v>
+        <v>4580</v>
       </c>
       <c r="K56" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -62766,7 +62766,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.09291773525350168</v>
+        <v>-0.09698764238450615</v>
       </c>
       <c r="E57" t="n">
         <v>4</v>
@@ -66280,7 +66280,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>14529</v>
@@ -69347,7 +69347,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -71970,7 +71970,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -75074,7 +75074,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -78622,7 +78622,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>104677</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -14693,7 +14693,7 @@
         <v>25883</v>
       </c>
       <c r="K56" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57">
@@ -24634,7 +24634,7 @@
         <v>1902</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -37898,10 +37898,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1723</v>
+        <v>1726</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -59202,7 +59202,7 @@
         <v>4226</v>
       </c>
       <c r="K56" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">
@@ -78637,10 +78637,10 @@
         <v>0.07986283348070826</v>
       </c>
       <c r="J56" t="n">
-        <v>12405</v>
+        <v>12471</v>
       </c>
       <c r="K56" t="n">
-        <v>83</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -14693,7 +14693,7 @@
         <v>25883</v>
       </c>
       <c r="K56" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57">
@@ -24634,7 +24634,7 @@
         <v>1902</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -59202,7 +59202,7 @@
         <v>4226</v>
       </c>
       <c r="K56" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
@@ -62750,7 +62750,7 @@
         <v>4580</v>
       </c>
       <c r="K56" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
@@ -78640,7 +78640,7 @@
         <v>12471</v>
       </c>
       <c r="K56" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -14693,7 +14693,7 @@
         <v>25883</v>
       </c>
       <c r="K56" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57">
@@ -59202,7 +59202,7 @@
         <v>4226</v>
       </c>
       <c r="K56" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
@@ -62750,7 +62750,7 @@
         <v>4580</v>
       </c>
       <c r="K56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
@@ -78640,7 +78640,7 @@
         <v>12471</v>
       </c>
       <c r="K56" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4031,7 +4031,7 @@
         <v>0.002571860816944024</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -4046,10 +4046,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -7579,7 +7579,7 @@
         <v>0.006376456161863887</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>19069</v>
@@ -11127,7 +11127,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -11142,10 +11142,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -14675,7 +14675,7 @@
         <v>0.03883205812921697</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>182377</v>
@@ -14690,10 +14690,10 @@
         <v>0.6359744732977259</v>
       </c>
       <c r="J56" t="n">
-        <v>25883</v>
+        <v>25932</v>
       </c>
       <c r="K56" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -18223,7 +18223,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -21290,7 +21290,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F43" t="n">
         <v>4406</v>
@@ -24616,7 +24616,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>24863</v>
@@ -24631,10 +24631,10 @@
         <v>0.01283491095780523</v>
       </c>
       <c r="J56" t="n">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -27683,7 +27683,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -30787,7 +30787,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -34335,7 +34335,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -37883,7 +37883,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -41431,7 +41431,7 @@
         <v>0.08481848934093128</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>36442</v>
@@ -41446,10 +41446,10 @@
         <v>0.3462835444472782</v>
       </c>
       <c r="J56" t="n">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="K56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -44979,7 +44979,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -48527,7 +48527,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -48542,10 +48542,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -52075,7 +52075,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -55623,7 +55623,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -55638,10 +55638,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="K56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -59184,7 +59184,7 @@
         <v>0.01003118423276034</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>62096</v>
@@ -62732,7 +62732,7 @@
         <v>0.003973791178790269</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>51839</v>
@@ -66280,7 +66280,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>14529</v>
@@ -66298,7 +66298,7 @@
         <v>5085</v>
       </c>
       <c r="K56" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
@@ -69347,7 +69347,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -71970,7 +71970,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -75074,7 +75074,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -78622,7 +78622,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>104677</v>
@@ -78640,7 +78640,7 @@
         <v>12471</v>
       </c>
       <c r="K56" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -14693,7 +14693,7 @@
         <v>25932</v>
       </c>
       <c r="K56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
@@ -34350,10 +34350,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="K56" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -44994,10 +44994,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K56" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57">
@@ -78640,7 +78640,7 @@
         <v>12471</v>
       </c>
       <c r="K56" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -11142,10 +11142,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>300827</v>
+        <v>300813</v>
       </c>
       <c r="C56" t="n">
         <v>9415</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.03883205812921697</v>
+        <v>0.03878517972844012</v>
       </c>
       <c r="E56" t="n">
         <v>6</v>
@@ -14709,7 +14709,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.1233456463019191</v>
+        <v>-0.1233060845571644</v>
       </c>
       <c r="E57" t="n">
         <v>4</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4031,7 +4031,7 @@
         <v>0.002571860816944024</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7579,7 +7579,7 @@
         <v>0.006376456161863887</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>19069</v>
@@ -7597,7 +7597,7 @@
         <v>1099</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -11127,7 +11127,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -11142,7 +11142,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -14675,25 +14675,25 @@
         <v>0.03878517972844012</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
-        <v>182377</v>
+        <v>182431</v>
       </c>
       <c r="G56" t="n">
         <v>4726</v>
       </c>
       <c r="H56" t="n">
-        <v>61305</v>
+        <v>40017</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.6359744732977259</v>
+        <v>0.4961308210562365</v>
       </c>
       <c r="J56" t="n">
         <v>25932</v>
       </c>
       <c r="K56" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57">
@@ -14724,7 +14724,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.3463817590415768</v>
+        <v>-0.2852879290763908</v>
       </c>
       <c r="J57" t="n">
         <v>18825</v>
@@ -18223,7 +18223,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -18241,7 +18241,7 @@
         <v>1403</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -21290,7 +21290,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F43" t="n">
         <v>4406</v>
@@ -24616,7 +24616,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>24863</v>
@@ -27683,7 +27683,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -30787,7 +30787,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -34335,7 +34335,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -37883,7 +37883,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -37901,7 +37901,7 @@
         <v>1726</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -41431,7 +41431,7 @@
         <v>0.08481848934093128</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>36442</v>
@@ -41446,10 +41446,10 @@
         <v>0.3462835444472782</v>
       </c>
       <c r="J56" t="n">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -44979,7 +44979,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -44997,7 +44997,7 @@
         <v>159</v>
       </c>
       <c r="K56" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">
@@ -48527,7 +48527,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -52075,7 +52075,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -55623,7 +55623,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -59184,7 +59184,7 @@
         <v>0.01003118423276034</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>62096</v>
@@ -59202,7 +59202,7 @@
         <v>4226</v>
       </c>
       <c r="K56" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57">
@@ -62732,7 +62732,7 @@
         <v>0.003973791178790269</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>51839</v>
@@ -62741,16 +62741,16 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>225</v>
+        <v>268</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.004243499729959108</v>
+        <v>0.005072911040814752</v>
       </c>
       <c r="J56" t="n">
         <v>4580</v>
       </c>
       <c r="K56" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
@@ -62781,7 +62781,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.8530846650276582</v>
+        <v>-0.8532059032375688</v>
       </c>
       <c r="J57" t="n">
         <v>2212</v>
@@ -66280,7 +66280,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>14529</v>
@@ -66298,7 +66298,7 @@
         <v>5085</v>
       </c>
       <c r="K56" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">
@@ -69347,7 +69347,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -71970,7 +71970,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -75074,7 +75074,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -78622,7 +78622,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>104677</v>
@@ -78637,10 +78637,10 @@
         <v>0.07986283348070826</v>
       </c>
       <c r="J56" t="n">
-        <v>12471</v>
+        <v>12508</v>
       </c>
       <c r="K56" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4031,7 +4031,7 @@
         <v>0.002571860816944024</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7579,7 +7579,7 @@
         <v>0.006376456161863887</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>19069</v>
@@ -11127,7 +11127,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
         <v>0.03878517972844012</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>182431</v>
@@ -18223,7 +18223,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -21290,7 +21290,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F43" t="n">
         <v>4406</v>
@@ -24616,7 +24616,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>24863</v>
@@ -27683,7 +27683,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -30787,7 +30787,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -34335,7 +34335,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -37883,7 +37883,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -41431,7 +41431,7 @@
         <v>0.08481848934093128</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>36442</v>
@@ -44979,7 +44979,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -48527,7 +48527,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -52075,7 +52075,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -55623,7 +55623,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -59184,7 +59184,7 @@
         <v>0.01003118423276034</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>62096</v>
@@ -62732,7 +62732,7 @@
         <v>0.003973791178790269</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>51839</v>
@@ -66280,7 +66280,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>14529</v>
@@ -69347,7 +69347,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -71970,7 +71970,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -75074,7 +75074,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -78622,7 +78622,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>104677</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
         <v>6.092731371473832e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>19069</v>
@@ -11497,7 +11497,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -15082,7 +15082,7 @@
         <v>0.03779132977175335</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>182431</v>
@@ -18667,7 +18667,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -21697,7 +21697,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>4406</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>24863</v>
@@ -28164,7 +28164,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -31379,7 +31379,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -34964,7 +34964,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -38549,7 +38549,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42134,7 +42134,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>36442</v>
@@ -45719,7 +45719,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -49304,7 +49304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -52889,7 +52889,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -56474,7 +56474,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -60072,7 +60072,7 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>62096</v>
@@ -63657,7 +63657,7 @@
         <v>0.003638899839281924</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>51839</v>
@@ -67242,7 +67242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>14529</v>
@@ -70272,7 +70272,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -72932,7 +72932,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -76147,7 +76147,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -79732,7 +79732,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>104677</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
         <v>6.092731371473832e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>19069</v>
@@ -11497,7 +11497,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -15082,7 +15082,7 @@
         <v>0.03779132977175335</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>182431</v>
@@ -18667,7 +18667,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -21697,7 +21697,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
         <v>4406</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>24863</v>
@@ -28164,7 +28164,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -31379,7 +31379,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -34964,7 +34964,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -38549,7 +38549,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42134,7 +42134,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>36442</v>
@@ -45719,7 +45719,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -49304,7 +49304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -52889,7 +52889,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -56474,7 +56474,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -60072,7 +60072,7 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>62096</v>
@@ -63657,7 +63657,7 @@
         <v>0.003638899839281924</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>51839</v>
@@ -67242,7 +67242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>14529</v>
@@ -70272,7 +70272,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -72932,7 +72932,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -76147,7 +76147,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -79732,7 +79732,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>104677</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15100,7 +15100,7 @@
         <v>25932</v>
       </c>
       <c r="K64" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65">
@@ -42152,7 +42152,7 @@
         <v>2949</v>
       </c>
       <c r="K64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -63675,7 +63675,7 @@
         <v>4580</v>
       </c>
       <c r="K64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65">
@@ -79750,7 +79750,7 @@
         <v>12508</v>
       </c>
       <c r="K64" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4345,7 +4345,7 @@
         <v>1123</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -42152,7 +42152,7 @@
         <v>2949</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -63675,7 +63675,7 @@
         <v>4580</v>
       </c>
       <c r="K64" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65">
@@ -79750,7 +79750,7 @@
         <v>12508</v>
       </c>
       <c r="K64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4345,7 +4345,7 @@
         <v>1123</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -42152,7 +42152,7 @@
         <v>2949</v>
       </c>
       <c r="K64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
@@ -63675,7 +63675,7 @@
         <v>4580</v>
       </c>
       <c r="K64" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
         <v>6.092731371473832e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>19069</v>
@@ -11497,7 +11497,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -15082,7 +15082,7 @@
         <v>0.03779132977175335</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>182431</v>
@@ -15097,10 +15097,10 @@
         <v>0.2483185334974503</v>
       </c>
       <c r="J64" t="n">
-        <v>25932</v>
+        <v>25987</v>
       </c>
       <c r="K64" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65">
@@ -18667,7 +18667,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -21697,7 +21697,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
         <v>4406</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>24863</v>
@@ -28164,7 +28164,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -31379,7 +31379,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -34964,7 +34964,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -38549,7 +38549,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -38567,7 +38567,7 @@
         <v>1726</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -42134,7 +42134,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>36442</v>
@@ -42152,7 +42152,7 @@
         <v>2949</v>
       </c>
       <c r="K64" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">
@@ -45719,7 +45719,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -49304,7 +49304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -52889,7 +52889,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -56474,7 +56474,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -60072,7 +60072,7 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>62096</v>
@@ -60090,7 +60090,7 @@
         <v>4226</v>
       </c>
       <c r="K64" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65">
@@ -63657,7 +63657,7 @@
         <v>0.003638899839281924</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>51839</v>
@@ -67242,7 +67242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>14529</v>
@@ -67260,7 +67260,7 @@
         <v>5085</v>
       </c>
       <c r="K64" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
@@ -70272,7 +70272,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -72932,7 +72932,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -76147,7 +76147,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -79732,7 +79732,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>104677</v>
@@ -79750,7 +79750,7 @@
         <v>12508</v>
       </c>
       <c r="K64" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
         <v>6.092731371473832e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>19069</v>
@@ -11497,7 +11497,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -15082,7 +15082,7 @@
         <v>0.03779132977175335</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>182431</v>
@@ -15100,7 +15100,7 @@
         <v>25987</v>
       </c>
       <c r="K64" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65">
@@ -18667,7 +18667,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -21697,7 +21697,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F49" t="n">
         <v>4406</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>24863</v>
@@ -28164,7 +28164,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -31379,7 +31379,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -34964,7 +34964,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -38549,7 +38549,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -38567,7 +38567,7 @@
         <v>1726</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -42134,7 +42134,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>36442</v>
@@ -45719,7 +45719,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -49304,7 +49304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -52889,7 +52889,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -56474,7 +56474,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -60072,7 +60072,7 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>62096</v>
@@ -63657,7 +63657,7 @@
         <v>0.003638899839281924</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>51839</v>
@@ -67242,7 +67242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>14529</v>
@@ -67260,7 +67260,7 @@
         <v>5085</v>
       </c>
       <c r="K64" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65">
@@ -70272,7 +70272,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -72932,7 +72932,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -76147,7 +76147,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -79732,7 +79732,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>104677</v>
@@ -79750,7 +79750,7 @@
         <v>12508</v>
       </c>
       <c r="K64" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -11515,7 +11515,7 @@
         <v>741</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -15100,7 +15100,7 @@
         <v>25987</v>
       </c>
       <c r="K64" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65">
@@ -79750,7 +79750,7 @@
         <v>12508</v>
       </c>
       <c r="K64" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
         <v>6.092731371473832e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>19069</v>
@@ -11497,7 +11497,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -15082,7 +15082,7 @@
         <v>0.03779132977175335</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>182431</v>
@@ -15100,7 +15100,7 @@
         <v>25987</v>
       </c>
       <c r="K64" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65">
@@ -18667,7 +18667,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -21697,7 +21697,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F49" t="n">
         <v>4406</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>24863</v>
@@ -28164,7 +28164,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -31379,7 +31379,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -34964,7 +34964,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -38549,7 +38549,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42134,7 +42134,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>36442</v>
@@ -42152,7 +42152,7 @@
         <v>2949</v>
       </c>
       <c r="K64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65">
@@ -45719,7 +45719,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -49304,7 +49304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -52889,7 +52889,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -56474,7 +56474,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -60072,7 +60072,7 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>62096</v>
@@ -63657,7 +63657,7 @@
         <v>0.003638899839281924</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>51839</v>
@@ -63675,7 +63675,7 @@
         <v>4580</v>
       </c>
       <c r="K64" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65">
@@ -67242,7 +67242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>14529</v>
@@ -70272,7 +70272,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -72932,7 +72932,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -76147,7 +76147,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -79732,7 +79732,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>104677</v>
@@ -79750,7 +79750,7 @@
         <v>12508</v>
       </c>
       <c r="K64" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
         <v>6.092731371473832e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>19069</v>
@@ -7930,7 +7930,7 @@
         <v>1099</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -11497,7 +11497,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -15082,7 +15082,7 @@
         <v>0.03779132977175335</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>182431</v>
@@ -15100,7 +15100,7 @@
         <v>25987</v>
       </c>
       <c r="K64" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65">
@@ -18667,7 +18667,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -21697,7 +21697,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
         <v>4406</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>24863</v>
@@ -28164,7 +28164,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -31379,7 +31379,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -34964,7 +34964,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -38549,7 +38549,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42134,7 +42134,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>36442</v>
@@ -45719,7 +45719,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -49304,7 +49304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -52889,7 +52889,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -56474,7 +56474,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -60072,7 +60072,7 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>62096</v>
@@ -63657,7 +63657,7 @@
         <v>0.003638899839281924</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>51839</v>
@@ -63675,7 +63675,7 @@
         <v>4580</v>
       </c>
       <c r="K64" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65">
@@ -67242,7 +67242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>14529</v>
@@ -70272,7 +70272,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -72932,7 +72932,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -76147,7 +76147,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -79732,7 +79732,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>104677</v>
@@ -79750,7 +79750,7 @@
         <v>12508</v>
       </c>
       <c r="K64" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
         <v>6.092731371473832e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>19069</v>
@@ -11497,7 +11497,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -15082,7 +15082,7 @@
         <v>0.03779132977175335</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>182431</v>
@@ -15100,7 +15100,7 @@
         <v>25987</v>
       </c>
       <c r="K64" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65">
@@ -18667,7 +18667,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -21697,7 +21697,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F49" t="n">
         <v>4406</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>24863</v>
@@ -28164,7 +28164,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -31379,7 +31379,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -34964,7 +34964,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -38549,7 +38549,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42134,7 +42134,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>36442</v>
@@ -45719,7 +45719,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -49304,7 +49304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -52889,7 +52889,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -56474,7 +56474,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -60072,7 +60072,7 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>62096</v>
@@ -63657,7 +63657,7 @@
         <v>0.003638899839281924</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>51839</v>
@@ -67242,7 +67242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>14529</v>
@@ -70272,7 +70272,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -72932,7 +72932,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -76147,7 +76147,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -79732,7 +79732,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>104677</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
         <v>6.092731371473832e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>19069</v>
@@ -11497,7 +11497,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -11512,7 +11512,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
@@ -15082,7 +15082,7 @@
         <v>0.03779132977175335</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>182431</v>
@@ -15100,7 +15100,7 @@
         <v>25987</v>
       </c>
       <c r="K64" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65">
@@ -18667,7 +18667,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -21697,7 +21697,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F49" t="n">
         <v>4406</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>24863</v>
@@ -28164,7 +28164,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -31379,7 +31379,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -34964,7 +34964,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -38549,7 +38549,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42134,7 +42134,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>36442</v>
@@ -42152,7 +42152,7 @@
         <v>2949</v>
       </c>
       <c r="K64" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65">
@@ -45719,7 +45719,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -49304,7 +49304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -52889,7 +52889,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -56474,7 +56474,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -60072,7 +60072,7 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>62096</v>
@@ -63657,7 +63657,7 @@
         <v>0.003638899839281924</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>51839</v>
@@ -67242,7 +67242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>14529</v>
@@ -70272,7 +70272,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -72932,7 +72932,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -76147,7 +76147,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -79732,7 +79732,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>104677</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
         <v>6.092731371473832e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>19069</v>
@@ -11497,7 +11497,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -15082,7 +15082,7 @@
         <v>0.03779132977175335</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>182431</v>
@@ -15100,7 +15100,7 @@
         <v>25987</v>
       </c>
       <c r="K64" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65">
@@ -18667,7 +18667,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -18685,7 +18685,7 @@
         <v>1403</v>
       </c>
       <c r="K64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -21697,7 +21697,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F49" t="n">
         <v>4406</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>24863</v>
@@ -28164,7 +28164,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -31379,7 +31379,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -34964,7 +34964,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -38549,7 +38549,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42134,7 +42134,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>36442</v>
@@ -45719,7 +45719,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -49304,7 +49304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -52889,7 +52889,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -56474,7 +56474,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -60072,25 +60072,25 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
-        <v>62096</v>
+        <v>61122</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>3488</v>
+        <v>4766</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.06484818964117552</v>
+        <v>0.06978405585322292</v>
       </c>
       <c r="J64" t="n">
         <v>4226</v>
       </c>
       <c r="K64" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65">
@@ -60121,7 +60121,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>-0.7228592339595024</v>
+        <v>-0.7241379310344828</v>
       </c>
       <c r="J65" t="n">
         <v>3271</v>
@@ -63657,7 +63657,7 @@
         <v>0.003638899839281924</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>51839</v>
@@ -67242,7 +67242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>14529</v>
@@ -70272,7 +70272,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -72932,7 +72932,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -76147,7 +76147,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -79732,7 +79732,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>104677</v>
@@ -79750,7 +79750,7 @@
         <v>12508</v>
       </c>
       <c r="K64" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65">
